--- a/blooms/conf.xlsx
+++ b/blooms/conf.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vsena\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45a9ac2dc34db9aa/Desktop/blooms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9EF7FFC-4163-457D-AED7-31C93EE8CC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A9EF7FFC-4163-457D-AED7-31C93EE8CC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{539F5124-E26B-4469-AB76-B57C52DEC705}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1138B070-F675-4E48-8650-1A87A4449C70}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1138B070-F675-4E48-8650-1A87A4449C70}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -487,10 +487,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502D78E5-50E9-45F1-9BA7-D173AA25BCEF}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="1" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="1" customWidth="1"/>
+    <col min="19" max="19" width="0.140625" customWidth="1"/>
+    <col min="20" max="20" width="0.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -582,7 +590,7 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -624,7 +632,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -666,7 +674,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -708,7 +716,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C6" s="3">
         <f>SUM(C2:C5)</f>
         <v>39</v>
